--- a/artfynd/S 3830-2021 artfynd.xlsx
+++ b/artfynd/S 3830-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210361</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210357</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210359</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/181007</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210355</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
           <t>Projekt Östergötland Flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118007605</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177246</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177274</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210353</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
           <t>Äldre fynd i Östergötlands flora x</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/423992</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,6 +1881,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/425946</t>
         </is>
       </c>
     </row>
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210351</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127319172</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210350</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2266,6 +2341,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/911068</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2380,6 +2460,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/911070</t>
         </is>
       </c>
     </row>
@@ -2482,6 +2567,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177267</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2582,6 +2672,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177244</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2682,6 +2777,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177243</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,6 +2882,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177268</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127319201</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3036,6 +3146,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127336135</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3153,6 +3268,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127335707</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3258,6 +3378,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6975657</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3356,6 +3481,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103809356</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3465,6 +3595,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121490849</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3594,6 +3729,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121490868</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3710,6 +3850,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1986363</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3809,6 +3954,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210354</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3908,6 +4058,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177271</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4010,6 +4165,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2244308</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4109,6 +4269,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210345</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4199,6 +4364,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210360</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4315,6 +4485,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1892633</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4414,6 +4589,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17210358</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4521,6 +4701,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103813200</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4663,6 +4848,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127336169</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4794,6 +4984,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127335681</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4925,6 +5120,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127335695</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5047,6 +5247,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127319542</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5162,6 +5367,11 @@
           <t>Projekt Östergötland Flora</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118007524</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5284,6 +5494,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127335486</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5399,6 +5614,11 @@
           <t>Projekt Östergötland Flora</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118007632</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5514,6 +5734,11 @@
           <t>Projekt Östergötland Flora</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118007625</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5615,6 +5840,11 @@
           <t>Äldre fynd i Östergötlands flora x</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3766902</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5728,6 +5958,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118007518</t>
         </is>
       </c>
     </row>
@@ -5830,6 +6065,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16593464</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5936,6 +6176,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72708267</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6037,6 +6282,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107453749</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6159,6 +6409,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127335379</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6259,6 +6514,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16593574</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6359,6 +6619,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16593578</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6461,6 +6726,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102939562</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6560,6 +6830,11 @@
       <c r="AY55" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107453747</t>
         </is>
       </c>
     </row>
@@ -6662,6 +6937,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177242</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6762,8 +7042,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16177263</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>